--- a/reports/excel/비상장_2026-04_W15.xlsx
+++ b/reports/excel/비상장_2026-04_W15.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="비상장_누적" sheetId="1" r:id="rId1"/>
-    <sheet name="가격변동알림" sheetId="2" r:id="rId2"/>
+    <sheet name="회사프로파일" sheetId="2" r:id="rId2"/>
+    <sheet name="가격변동알림" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z28"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.03515625" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.03515625" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="50.83203125" customWidth="1"/>
+    <col min="20" max="20" width="50.83203125" customWidth="1"/>
+    <col min="21" max="21" width="50.83203125" customWidth="1"/>
+    <col min="22" max="22" width="50.83203125" customWidth="1"/>
+    <col min="23" max="23" width="50.83203125" customWidth="1"/>
+    <col min="24" max="24" width="50.83203125" customWidth="1"/>
+    <col min="25" max="25" width="50.83203125" customWidth="1"/>
+    <col min="26" max="26" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,73 +437,73 @@
         <v>회사명</v>
       </c>
       <c r="C1" t="str">
-        <v>업종</v>
+        <v>섹터</v>
       </c>
       <c r="D1" t="str">
-        <v>DART상태</v>
+        <v>성장성등급</v>
       </c>
       <c r="E1" t="str">
-        <v>매력도</v>
+        <v>매력도점수</v>
       </c>
       <c r="F1" t="str">
-        <v>설립연도</v>
+        <v>점수세부내역</v>
       </c>
       <c r="G1" t="str">
-        <v>대표자</v>
+        <v>평가등급</v>
       </c>
       <c r="H1" t="str">
-        <v>주요제품</v>
+        <v>노출이유</v>
       </c>
       <c r="I1" t="str">
-        <v>추정기업가치_억</v>
+        <v>최신라운드</v>
       </c>
       <c r="J1" t="str">
-        <v>최신라운드</v>
+        <v>투자금액(억)</v>
       </c>
       <c r="K1" t="str">
-        <v>투자금액_억</v>
+        <v>밸류에이션(억)</v>
       </c>
       <c r="L1" t="str">
-        <v>밸류에이션_억</v>
+        <v>적정밸류(억)</v>
       </c>
       <c r="M1" t="str">
-        <v>누적투자_억</v>
+        <v>저평가율(%)</v>
       </c>
       <c r="N1" t="str">
-        <v>밸류상승률</v>
+        <v>누적투자총액(억)</v>
       </c>
       <c r="O1" t="str">
+        <v>참여VC</v>
+      </c>
+      <c r="P1" t="str">
         <v>38커뮤니케이션</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>증권플러스</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>특허수</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>강점1</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>강점2</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>강점3</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>리스크1</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>리스크2</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>리스크3</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Y1" t="str">
         <v>IPO전망</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>노출이유</v>
       </c>
       <c r="Z1" t="str">
         <v>출처링크</v>
@@ -485,93 +514,93 @@
         <v>2026-04-06</v>
       </c>
       <c r="B2" t="str">
-        <v>오픈엣지</v>
+        <v>넥서스비</v>
       </c>
       <c r="C2" t="str">
         <v>IT</v>
       </c>
       <c r="D2" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2019</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>이성현</v>
+        <v>-</v>
       </c>
       <c r="H2" t="str">
-        <v>온디바이스 AI 반도체 NPU IP 설계 및 엣지 AI 솔루션 제공</v>
+        <v>[더벨]넥서스비, 100억 시리즈C 돌입…산업은행 베팅</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>시리즈C</v>
       </c>
       <c r="J2" t="str">
-        <v>추가 투자 (유상증자)</v>
+        <v>100</v>
       </c>
       <c r="K2" t="str">
-        <v>비공개</v>
+        <v/>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>비공개</v>
+        <v/>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>100+</v>
       </c>
       <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>0</v>
       </c>
-      <c r="R2" t="str">
-        <v>온디바이스 AI 및 엣지 AI 반도체 IP 분야 기술 전문성 보유로 AI 산업 성장 수혜 기대</v>
-      </c>
       <c r="S2" t="str">
-        <v>에이티넘인베스트먼트 등 국내 주요 VC로부터 지속적인 추가 투자 유치로 투자자 신뢰 확인</v>
+        <v>산업은행이 시리즈C에 직접 베팅하며 기관 신뢰도 확보</v>
       </c>
       <c r="T2" t="str">
-        <v>글로벌 NPU IP 시장 성장과 함께 팹리스·AI 반도체 수요 증가로 시장 성장성 높음</v>
+        <v>시리즈C 단계 진입으로 사업 모델의 일정 수준 검증 완료</v>
       </c>
       <c r="U2" t="str">
-        <v>재무정보 미공개로 매출·수익성 등 기초 펀더멘털 검증 불가</v>
+        <v>100억 규모의 신규 자금 조달로 성장 동력 확보 가능성</v>
       </c>
       <c r="V2" t="str">
-        <v>ARM, Cadence 등 글로벌 대형 반도체 IP 기업과의 경쟁 심화로 시장 확대 난항 가능성</v>
+        <v>재무정보 미공개로 수익성·매출 등 핵심 펀더멘털 검증 불가</v>
       </c>
       <c r="W2" t="str">
-        <v>특허 건수 0건으로 기록되어 핵심 기술 보호 체계 및 지식재산 경쟁력 불확실</v>
+        <v>특허 0건으로 기술 독자성 및 진입장벽 취약</v>
       </c>
       <c r="X2" t="str">
-        <v>AI 반도체 IP 섹터 관심 지속 및 VC 후속 투자 유치 흐름 감안 시 2026~2027년 코스닥 IPO 추진 가능성 있으나, 재무 공개 및 고객사 확보 성과가 관건</v>
+        <v>비상장 시장 가격 정보 부재 및 거래 활성도 낮아 유동성 리스크 존재</v>
       </c>
       <c r="Y2" t="str">
-        <v>[더벨][유증 디테일] 오픈엣지, 에이티넘인베로부터 추가 투자 유치</v>
+        <v>시리즈C 진행 중으로 IPO는 이르면 2027~2028년 가능하나, 재무정보 부재로 구체적 시점 예단 어려움</v>
       </c>
       <c r="Z2" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604031441473560106026</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021151163520108335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B3" t="str">
-        <v>닷</v>
+        <v>넥서스비</v>
       </c>
       <c r="C3" t="str">
         <v>기타</v>
       </c>
       <c r="D3" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E3">
         <v>4</v>
@@ -580,69 +609,69 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H3" t="str">
-        <v>시각장애인용 점자 스마트 기기 및 AI 기반 보조기술 솔루션 개발 소셜벤처</v>
+        <v>[더벨]넥서스비, 100억 시리즈C 돌입…산업은행 베팅</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>시리즈C</v>
       </c>
       <c r="J3" t="str">
-        <v>최근 투자 라운드</v>
+        <v>100</v>
       </c>
       <c r="K3" t="str">
-        <v>43</v>
+        <v/>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>43</v>
+        <v/>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>100+</v>
       </c>
       <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>0</v>
       </c>
-      <c r="R3" t="str">
-        <v>소셜벤처로서 시각장애인 보조기술 분야 사회적 가치와 ESG 투자 트렌드에 부합</v>
-      </c>
       <c r="S3" t="str">
-        <v>IPO 재도전 의지 확인으로 자본시장 접근성 및 성장 모멘텀 보유</v>
+        <v>국책금융기관인 산업은행이 시리즈C에 참여하여 신뢰도 및 안정성 확보</v>
       </c>
       <c r="T3" t="str">
-        <v>43억 신규 투자 유치를 통한 운영 자금 확보 및 투자자 신뢰 유지</v>
+        <v>시리즈C 단계 진입으로 일정 수준 이상의 사업 성숙도 및 트랙레코드 보유 추정</v>
       </c>
       <c r="U3" t="str">
-        <v>재무정보 미공개로 실적 및 수익성 검증 불가, 투자 불확실성 높음</v>
+        <v>100억 규모의 추가 자금 조달로 사업 확장 여력 확보</v>
       </c>
       <c r="V3" t="str">
-        <v>IPO 재도전 표현에서 이전 상장 시도 실패 이력이 암시되어 시장 수용성 우려</v>
+        <v>재무정보 미공개로 매출·손익 등 핵심 펀더멘털 검증 불가</v>
       </c>
       <c r="W3" t="str">
-        <v>특허 건수 0건으로 기술 보호 역량 및 독자적 IP 경쟁력 취약</v>
+        <v>특허 0건으로 기술적 해자 및 지식재산권 경쟁력 불명확</v>
       </c>
       <c r="X3" t="str">
-        <v>43억 투자 유치 후 IPO 재도전 전망이 언급되나, 이전 상장 실패 이력 및 재무정보 부재로 단기 상장보다는 2027년 이후 재추진 가능성이 높음</v>
+        <v>주요 사업 내용, 대표자, 설립연도 등 기본 정보 부재로 투자 판단 근거 부족</v>
       </c>
       <c r="Y3" t="str">
-        <v>[더벨]'소셜벤처' 닷, 43억 투자유치…IPO 재도전 전망</v>
+        <v>산업은행 투자 유치로 IPO 가능성은 존재하나 공개 정보 부족으로 구체적 시점 예측 어려움</v>
       </c>
       <c r="Z3" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021052204360105140</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021151163520108335</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B4" t="str">
         <v>넥서스비</v>
@@ -651,70 +680,70 @@
         <v>IT</v>
       </c>
       <c r="D4" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>투자라운드:13/15 | 투자금액:12/15 | 밸류에이션:0/10 | 참여VC티어:3/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:0/5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H4" t="str">
-        <v>B2B 기술 기반 솔루션 제공 기업 (정확한 제품·서비스 정보 확인 불가)</v>
+        <v>[더벨]넥서스비, 100억 시리즈C 돌입…산업은행 베팅</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>시리즈C</v>
       </c>
       <c r="J4" t="str">
-        <v>시리즈C</v>
+        <v>100</v>
       </c>
       <c r="K4" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>100+</v>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
       <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>0</v>
       </c>
-      <c r="R4" t="str">
-        <v>산업은행이 시리즈C에 직접 베팅하며 기관 신뢰도 확보</v>
-      </c>
       <c r="S4" t="str">
-        <v>시리즈C 단계 진입으로 사업 모델의 일정 수준 검증 완료</v>
+        <v>국책금융기관인 한국산업은행의 시리즈C 참여로 신뢰도 및 안정성 확보</v>
       </c>
       <c r="T4" t="str">
-        <v>100억 규모의 신규 자금 조달로 성장 동력 확보 가능성</v>
+        <v>시리즈C 단계 진입으로 일정 수준 이상의 사업 성숙도 및 매출 기반 보유 가능성</v>
       </c>
       <c r="U4" t="str">
-        <v>재무정보 미공개로 수익성·매출 등 핵심 펀더멘털 검증 불가</v>
+        <v>비상장 거래소(38커뮤니케이션)에 등록되어 있어 유동성 및 시장 인지도 존재</v>
       </c>
       <c r="V4" t="str">
-        <v>특허 0건으로 기술 독자성 및 진입장벽 취약</v>
+        <v>재무정보 미공개로 매출·수익성 등 핵심 지표 검증 불가</v>
       </c>
       <c r="W4" t="str">
-        <v>비상장 시장 가격 정보 부재 및 거래 활성도 낮아 유동성 리스크 존재</v>
+        <v>특허 0건으로 기술 독점성 및 지식재산권 기반 경쟁 우위 취약</v>
       </c>
       <c r="X4" t="str">
-        <v>시리즈C 진행 중으로 IPO는 이르면 2027~2028년 가능하나, 재무정보 부재로 구체적 시점 예단 어려움</v>
+        <v>비상장 가격 데이터 불완전(거래량·가격 미확인)으로 시장 평가 불투명</v>
       </c>
       <c r="Y4" t="str">
-        <v>[더벨]넥서스비, 100억 시리즈C 돌입…산업은행 베팅</v>
+        <v>산업은행 참여로 시리즈C 완료 시 IPO 추진 가능성 있으나, 재무정보 부재로 구체적 시점 예측 어려움</v>
       </c>
       <c r="Z4" t="str">
         <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021151163520108335</v>
@@ -725,111 +754,111 @@
         <v>2026-04-06</v>
       </c>
       <c r="B5" t="str">
-        <v>스탁키퍼</v>
+        <v>닷</v>
       </c>
       <c r="C5" t="str">
-        <v>핀테크</v>
+        <v>기타</v>
       </c>
       <c r="D5" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H5" t="str">
-        <v>한우 조각투자 플랫폼 '뱅카우' 운영</v>
+        <v>[더벨]'소셜벤처' 닷, 43억 투자유치…IPO 재도전 전망</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>최근 투자 라운드</v>
       </c>
       <c r="J5" t="str">
-        <v>시리즈B</v>
+        <v>43</v>
       </c>
       <c r="K5" t="str">
-        <v>70</v>
+        <v/>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>70</v>
+        <v/>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>43</v>
       </c>
       <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>0</v>
       </c>
-      <c r="R5" t="str">
-        <v>한우 조각투자라는 독특한 실물자산 기반 핀테크 니치 시장 선점</v>
-      </c>
       <c r="S5" t="str">
-        <v>시리즈B 클로징으로 성장 단계 진입 및 투자자 신뢰 확보</v>
+        <v>소셜벤처로서 시각장애인 보조기술 분야 사회적 가치와 ESG 투자 트렌드에 부합</v>
       </c>
       <c r="T5" t="str">
-        <v>농축산업과 금융기술의 결합으로 차별화된 비즈니스 모델 구축</v>
+        <v>IPO 재도전 의지 확인으로 자본시장 접근성 및 성장 모멘텀 보유</v>
       </c>
       <c r="U5" t="str">
-        <v>한우 가격 변동성 및 구제역 등 농축산 관련 외부 리스크에 직접 노출</v>
+        <v>43억 신규 투자 유치를 통한 운영 자금 확보 및 투자자 신뢰 유지</v>
       </c>
       <c r="V5" t="str">
-        <v>조각투자 관련 금융규제 불확실성으로 사업 지속성 위협 가능</v>
+        <v>재무정보 미공개로 실적 및 수익성 검증 불가, 투자 불확실성 높음</v>
       </c>
       <c r="W5" t="str">
-        <v>특허 0건으로 기술 경쟁력 및 진입장벽이 취약하고 모방 가능성 존재</v>
+        <v>IPO 재도전 표현에서 이전 상장 시도 실패 이력이 암시되어 시장 수용성 우려</v>
       </c>
       <c r="X5" t="str">
-        <v>시리즈B 초기 단계로 IPO까지 상당한 시간이 필요하며, 규제 환경 안정화 및 수익성 확보 후 빠르면 2027~2028년경 가능성 검토 예상</v>
+        <v>특허 건수 0건으로 기술 보호 역량 및 독자적 IP 경쟁력 취약</v>
       </c>
       <c r="Y5" t="str">
-        <v>[더벨]'뱅카우' 스탁키퍼, 70억 시리즈B 라운드 클로징</v>
+        <v>43억 투자 유치 후 IPO 재도전 전망이 언급되나, 이전 상장 실패 이력 및 재무정보 부재로 단기 상장보다는 2027년 이후 재추진 가능성이 높음</v>
       </c>
       <c r="Z5" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011547179320109662</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021052204360105140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B6" t="str">
-        <v>블룸에이아이</v>
+        <v>닷</v>
       </c>
       <c r="C6" t="str">
         <v>IT</v>
       </c>
       <c r="D6" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>김범수, 박진영</v>
+        <v>-</v>
       </c>
       <c r="H6" t="str">
-        <v>AI 기반 서비스 개발 및 제공 (밸류업 인터뷰 기반 추정)</v>
+        <v>[더벨]'소셜벤처' 닷, 43억 투자유치…IPO 재도전 전망</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>최근 투자 라운드</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>43</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -841,75 +870,75 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>43</v>
       </c>
       <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>0</v>
       </c>
-      <c r="R6" t="str">
-        <v>공동대표 체제로 더벨 인터뷰 노출 — 기관 투자자 대상 밸류업 활동 진행 중</v>
-      </c>
       <c r="S6" t="str">
-        <v>AI 분야 포지셔닝으로 현재 시장 트렌드에 부합하는 업종</v>
+        <v>소셜벤처로서 사회적 가치와 비즈니스 가치를 동시에 추구하는 차별화된 포지셔닝</v>
       </c>
       <c r="T6" t="str">
-        <v>비상장주식 플랫폼(38커뮤니케이션 등)에 등록되어 유동성 확보 시도 중</v>
+        <v>43억 신규 투자유치 성공으로 IPO 재도전을 위한 자금 확보</v>
       </c>
       <c r="U6" t="str">
-        <v>재무정보 전무 — 매출, 영업이익 등 핵심 지표 확인 불가</v>
+        <v>접근성 기술 분야의 글로벌 시장 확장 가능성 및 ESG 트렌드 부합</v>
       </c>
       <c r="V6" t="str">
-        <v>특허 0건 — 기술 독자성 및 IP 경쟁력 검증 어려움</v>
+        <v>IPO '재도전' 표현에서 알 수 있듯 이전 상장 시도 실패 이력 존재</v>
       </c>
       <c r="W6" t="str">
-        <v>비상장 거래 데이터 부족(거래량·가격 미형성) — 시장 내 인지도 및 유동성 극히 낮음</v>
+        <v>재무정보 미공개로 수익성 및 매출 규모 검증 불가</v>
       </c>
       <c r="X6" t="str">
-        <v>공개된 투자 이력·재무 데이터가 없어 IPO 시점 예측 불가, 밸류업 인터뷰 활동을 감안하면 중장기(3년 이상) 준비 단계로 추정</v>
+        <v>비상장 거래가 신한스팩18호와 연계된 스팩 합병 방식으로, 자체 상장 경쟁력 불확실</v>
       </c>
       <c r="Y6" t="str">
-        <v>[더벨][thebell interview | 블룸에이아이 밸류업] 김범수·박진영 대표 ...</v>
+        <v>신한스팩18호를 통한 스팩 합병 상장 방식으로 IPO 재도전 중이며, 2026년 내 상장 가시화 가능성 있으나 과거 실패 이력으로 불확실성 상존</v>
       </c>
       <c r="Z6" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202603311441089560102228</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021052204360105140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B7" t="str">
-        <v>메이사</v>
+        <v>닷</v>
       </c>
       <c r="C7" t="str">
-        <v>IT</v>
+        <v>기타</v>
       </c>
       <c r="D7" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>투자라운드:0/15 | 투자금액:6/15 | 밸류에이션:0/10 | 참여VC티어:0/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:5/5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H7" t="str">
-        <v>공간정보 AI 기반 3D 지도·디지털 트윈 솔루션 제공</v>
+        <v>[더벨]'소셜벤처' 닷, 43억 투자유치…IPO 재도전 전망</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>최근 투자라운드</v>
       </c>
       <c r="J7" t="str">
-        <v>신규 투자 라운드</v>
+        <v>43</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -921,43 +950,43 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>43</v>
       </c>
       <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>0</v>
       </c>
-      <c r="R7" t="str">
-        <v>공간정보 AI 및 디지털 트윈 분야는 스마트시티·자율주행·국방 등 수요가 빠르게 확대되는 고성장 섹터</v>
-      </c>
       <c r="S7" t="str">
-        <v>타임폴리오(운용규모 상위권 헤지펀드)로부터 신규 투자 유치, 기관 신뢰도 확보</v>
+        <v>소셜벤처로서 사회적 가치와 비즈니스 가치를 동시에 추구하는 차별화된 포지셔닝</v>
       </c>
       <c r="T7" t="str">
-        <v>공간정보 AI는 정부 주도 디지털 인프라 정책(국토부, 스마트시티 등)과 정책 수혜 가능성 높음</v>
+        <v>43억 원 신규 투자 유치로 IPO 재도전을 위한 자금 확보</v>
       </c>
       <c r="U7" t="str">
-        <v>공개된 재무 정보 전무로 매출·수익성·성장률 검증 불가</v>
+        <v>신한스팩18호를 통한 스팩 합병 IPO 경로 모색 중으로 상장 가시성 존재</v>
       </c>
       <c r="V7" t="str">
-        <v>특허 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡하거나 공개되지 않은 상태</v>
+        <v>과거 IPO 도전 실패 이력이 있어 재도전 성공 여부 불확실</v>
       </c>
       <c r="W7" t="str">
-        <v>비상장 거래 데이터가 신한스팩18호 항목에 혼재되어 있어 실제 유통 시장 형성 여부 불명확</v>
+        <v>재무정보 미공개로 수익성·매출 규모 파악 불가</v>
       </c>
       <c r="X7" t="str">
-        <v>스팩 관련 데이터가 일부 노출되어 스팩 합병 상장 가능성이 있으나, 재무·기술 정보 부족으로 구체적 시점 예단 어려움</v>
+        <v>특허 건수 0건으로 기술적 해자(Moat) 확인 어려움</v>
       </c>
       <c r="Y7" t="str">
-        <v>타임폴리오, '공간정보 AI 기업' 메이사에 신규 투자 [fn마켓워치]</v>
+        <v>신한스팩18호와의 합병을 통한 IPO 재도전 가능성이 있으며, 43억 투자유치를 발판으로 2026년 내 상장 추진이 예상되나 불확실성 존재</v>
       </c>
       <c r="Z7" t="str">
-        <v>http://www.fnnews.com/news/202604021510288489</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021052204360105140</v>
       </c>
     </row>
     <row r="8">
@@ -971,70 +1000,70 @@
         <v>IT</v>
       </c>
       <c r="D8" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" t="str">
-        <v>2020</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>박성현</v>
+        <v>-</v>
       </c>
       <c r="H8" t="str">
-        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 스타트업</v>
+        <v>[더벨][VC 인사 풍향계] SV인베, VC조직 통합…오탁근·강민구·이효상 ...</v>
       </c>
       <c r="I8" t="str">
+        <v>시리즈C</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1000</v>
+      </c>
+      <c r="K8" t="str">
         <v>10000</v>
       </c>
-      <c r="J8" t="str">
-        <v>시리즈C</v>
-      </c>
-      <c r="K8" t="str">
-        <v>1000</v>
-      </c>
       <c r="L8" t="str">
-        <v>10000</v>
+        <v/>
       </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>약 1400</v>
       </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
       <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>0</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <v>국내 대표 AI 반도체(NPU) 팹리스 스타트업으로 기술력 인정</v>
       </c>
-      <c r="S8" t="str">
+      <c r="T8" t="str">
         <v>SV인베스트먼트 등 주요 VC로부터 지속적인 투자 유치 성공</v>
       </c>
-      <c r="T8" t="str">
+      <c r="U8" t="str">
         <v>AI 인프라 수요 급증에 따른 NPU 시장 성장 수혜 가능성</v>
       </c>
-      <c r="U8" t="str">
+      <c r="V8" t="str">
         <v>수집 데이터 부족으로 재무정보 및 구체적 투자 이력 확인 불가</v>
       </c>
-      <c r="V8" t="str">
+      <c r="W8" t="str">
         <v>엔비디아, 퀄컴 등 글로벌 빅테크와의 극심한 경쟁 환경</v>
       </c>
-      <c r="W8" t="str">
+      <c r="X8" t="str">
         <v>팹리스 특성상 외부 파운드리 의존도 높아 공급망 리스크 존재</v>
       </c>
-      <c r="X8" t="str">
+      <c r="Y8" t="str">
         <v>AI 반도체 시장 성장세에 힘입어 2025~2026년 내 IPO 추진 가능성 있으나, 수집 데이터 부족으로 구체적 시점 판단 어려움</v>
-      </c>
-      <c r="Y8" t="str">
-        <v>[더벨][VC 인사 풍향계] SV인베, VC조직 통합…오탁근·강민구·이효상 ...</v>
       </c>
       <c r="Z8" t="str">
         <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021525063440101161</v>
@@ -1042,16 +1071,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B9" t="str">
-        <v>프로티어바이오텍</v>
+        <v>리벨리온</v>
       </c>
       <c r="C9" t="str">
-        <v>바이오</v>
+        <v>IT</v>
       </c>
       <c r="D9" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E9">
         <v>4</v>
@@ -1060,64 +1089,64 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H9" t="str">
-        <v>분자접착제(Molecular Glue) 및 DAC(분해유도 항체접합체) 기반 신약 개발</v>
+        <v>[더벨][VC 인사 풍향계] SV인베, VC조직 통합…오탁근·강민구·이효상 ...</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>시리즈C</v>
       </c>
       <c r="J9" t="str">
-        <v>Pre-A</v>
+        <v>1000</v>
       </c>
       <c r="K9" t="str">
-        <v>35</v>
+        <v/>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>35</v>
+        <v/>
       </c>
       <c r="N9" t="str">
         <v/>
       </c>
       <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>0</v>
       </c>
-      <c r="R9" t="str">
-        <v>분자접착제 및 DAC 등 글로벌 신약 트렌드에 부합하는 혁신 플랫폼 기술 보유</v>
-      </c>
       <c r="S9" t="str">
-        <v>표적단백질분해(TPD) 분야는 글로벌 빅파마의 높은 관심과 대형 기술이전 사례가 다수 존재하는 고성장 시장</v>
+        <v>AI 반도체(NPU) 분야 국내 선도 팹리스 기업으로 기술 경쟁력 보유</v>
       </c>
       <c r="T9" t="str">
-        <v>Pre-A 단계에서 35억 유치로 초기 사업화 자금 확보, 향후 추가 라운드 가능성 존재</v>
+        <v>SV인베스트먼트 등 주요 VC로부터 지속적인 투자 유치 이력</v>
       </c>
       <c r="U9" t="str">
-        <v>특허 등록 건수 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡하여 기술 방어력 취약</v>
+        <v>AI 인프라 수요 급증으로 NPU 시장 성장 수혜 가능성</v>
       </c>
       <c r="V9" t="str">
-        <v>재무정보 미공개로 매출·손익 현황 파악 불가, 투자 판단 근거 부족</v>
+        <v>수집 데이터 부족으로 재무정보·특허·밸류에이션 등 핵심 정보 확인 불가</v>
       </c>
       <c r="W9" t="str">
-        <v>Pre-A 초기 단계로 임상 진입까지 장기간 및 대규모 추가 자금 소요 예상, 밸류에이션 불확실성 높음</v>
+        <v>엔비디아·퀄컴 등 글로벌 AI 반도체 기업과의 극심한 경쟁</v>
       </c>
       <c r="X9" t="str">
-        <v>현재 Pre-A 초기 단계로 임상 데이터 축적 및 후속 투자 유치가 선행되어야 하며, IPO 가능성은 존재하나 최소 5년 이상 소요 예상</v>
+        <v>비상장 가격 데이터가 신한스팩18호 관련 정보와 혼재되어 기업 특정 신뢰도 낮음</v>
       </c>
       <c r="Y9" t="str">
-        <v>프로티어바이오텍, pre-A 35억..'분자접착제·DAC' 개발</v>
+        <v>수집 데이터 불충분으로 IPO 시점 특정 어려우나, AI 반도체 섹터 관심도 고려 시 2025~2026년 내 추진 가능성 존재</v>
       </c>
       <c r="Z9" t="str">
-        <v>https://www.biospectator.com/view/news_view.php?varAtcId=28333</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021525063440101161</v>
       </c>
     </row>
     <row r="10">
@@ -1125,114 +1154,114 @@
         <v>2026-04-06</v>
       </c>
       <c r="B10" t="str">
-        <v>퓨리오사AI</v>
+        <v>메이사</v>
       </c>
       <c r="C10" t="str">
         <v>IT</v>
       </c>
       <c r="D10" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="str">
-        <v>2017</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>백준호</v>
+        <v>-</v>
       </c>
       <c r="H10" t="str">
-        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
+        <v>타임폴리오, '공간정보 AI 기업' 메이사에 신규 투자 [fn마켓워치]</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>신규 투자 라운드</v>
       </c>
       <c r="J10" t="str">
-        <v>시리즈 D (교보증권 검토)</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>1000억 이하</v>
+        <v/>
       </c>
       <c r="L10" t="str">
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>미상</v>
+        <v/>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
       <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>0</v>
       </c>
-      <c r="R10" t="str">
-        <v>국내 독자 AI 반도체(NPU) 기술력 보유로 차별화된 팹리스 포지셔닝</v>
-      </c>
       <c r="S10" t="str">
-        <v>교보증권 등 기관 투자자의 지속적 투자 검토로 시장 신뢰도 확인</v>
+        <v>공간정보 AI 및 디지털 트윈 분야는 스마트시티·자율주행·국방 등 수요가 빠르게 확대되는 고성장 섹터</v>
       </c>
       <c r="T10" t="str">
-        <v>글로벌 AI 인프라 수요 급증에 따른 국산 AI 반도체 수요 증가 수혜 기대</v>
+        <v>타임폴리오(운용규모 상위권 헤지펀드)로부터 신규 투자 유치, 기관 신뢰도 확보</v>
       </c>
       <c r="U10" t="str">
-        <v>엔비디아 등 글로벌 빅테크와의 기술·자본력 격차로 시장 침투 어려움</v>
+        <v>공간정보 AI는 정부 주도 디지털 인프라 정책(국토부, 스마트시티 등)과 정책 수혜 가능성 높음</v>
       </c>
       <c r="V10" t="str">
-        <v>재무정보 미공개로 수익성 및 현금흐름 검증 불가</v>
+        <v>공개된 재무 정보 전무로 매출·수익성·성장률 검증 불가</v>
       </c>
       <c r="W10" t="str">
-        <v>AI 반도체 시장의 빠른 기술 변화로 제품 경쟁력 유지 불확실성 존재</v>
+        <v>특허 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡하거나 공개되지 않은 상태</v>
       </c>
       <c r="X10" t="str">
-        <v>국내 AI 반도체 대표 기업으로 관심은 높으나, 글로벌 경쟁 심화 및 수익화 검증 필요로 IPO는 2027~2028년 이후 가능성으로 전망</v>
+        <v>비상장 거래 데이터가 신한스팩18호 항목에 혼재되어 있어 실제 유통 시장 형성 여부 불명확</v>
       </c>
       <c r="Y10" t="str">
-        <v>[더벨]교보증권, 퓨리오사AI 투자 검토…1000억 이하 가닥</v>
+        <v>스팩 관련 데이터가 일부 노출되어 스팩 합병 상장 가능성이 있으나, 재무·기술 정보 부족으로 구체적 시점 예단 어려움</v>
       </c>
       <c r="Z10" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021616402280106871</v>
+        <v>http://www.fnnews.com/news/202604021510288489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B11" t="str">
-        <v>텔레픽스</v>
+        <v>메이사</v>
       </c>
       <c r="C11" t="str">
-        <v>기타</v>
+        <v>IT</v>
       </c>
       <c r="D11" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H11" t="str">
-        <v>우주·위성 통신 기술 기반 서비스 및 유럽 수출 사업</v>
+        <v>타임폴리오, '공간정보 AI 기업' 메이사에 신규 투자 [fn마켓워치]</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>신규 투자 (라운드 미상)</v>
       </c>
       <c r="J11" t="str">
-        <v>SBVA 투자 라운드</v>
+        <v>미공개</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>미공개</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -1241,43 +1270,43 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>미공개</v>
       </c>
       <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>0</v>
       </c>
-      <c r="R11" t="str">
-        <v>매출 0에서 유럽 수출까지 성장한 실적, 글로벌 시장 개척 능력 입증</v>
-      </c>
       <c r="S11" t="str">
-        <v>SBVA 등 주요 VC의 투자 유치로 사업성과 기술력 검증</v>
+        <v>공간정보 AI라는 틈새 기술 특화 분야로 차별화된 포지셔닝 가능</v>
       </c>
       <c r="T11" t="str">
-        <v>우주·위성 분야 성장 섹터 내 선도적 포지셔닝 가능성</v>
+        <v>타임폴리오 등 투자 전문기관의 신규 투자 유치로 외부 검증 확인</v>
       </c>
       <c r="U11" t="str">
-        <v>재무정보 미공개로 수익성 및 현금흐름 파악 불가</v>
+        <v>스마트시티·자율주행·디지털트윈 등 공간정보 수요 급성장 시장과 연계 가능성</v>
       </c>
       <c r="V11" t="str">
-        <v>특허 0건으로 핵심 기술 보호 체계 미흡, 경쟁사 모방 리스크 존재</v>
+        <v>재무정보 미공개로 매출·수익성 등 핵심 펀더멘털 파악 불가</v>
       </c>
       <c r="W11" t="str">
-        <v>우주항공 규제 환경 불확실성 및 정부 수요 의존도 리스크</v>
+        <v>특허 0건으로 기술 독점성 및 지식재산권 방어력이 취약</v>
       </c>
       <c r="X11" t="str">
-        <v>신한스팩18호와의 연관 정황이 있어 스팩 합병 상장 가능성이 있으나, 재무 정보 부재로 구체적 시점 예측 어려움</v>
+        <v>비상장 거래 데이터 부재(신한스팩18호 연계 가능성 언급만 있어 유동성 불투명)</v>
       </c>
       <c r="Y11" t="str">
-        <v>[더벨][VC x 스타트업 동행] '매출 0'에서 유럽 수출까지…SBVA·텔레픽스...</v>
+        <v>공간정보 AI 성장성은 긍정적이나 재무·특허 정보 부족으로 단기 IPO 가능성 판단 어려우며, 스팩 합병 경로 검토 중인 것으로 추정됨</v>
       </c>
       <c r="Z11" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011519406360102666</v>
+        <v>http://www.fnnews.com/news/202604021510288489</v>
       </c>
     </row>
     <row r="12">
@@ -1285,159 +1314,159 @@
         <v>2026-04-07</v>
       </c>
       <c r="B12" t="str">
-        <v>오픈엣지</v>
+        <v>메이사</v>
       </c>
       <c r="C12" t="str">
         <v>IT</v>
       </c>
       <c r="D12" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>2019</v>
+        <v>투자라운드:0/15 | 투자금액:0/15 | 밸류에이션:0/10 | 참여VC티어:3/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:2/5</v>
       </c>
       <c r="G12" t="str">
-        <v>이성현</v>
+        <v>-</v>
       </c>
       <c r="H12" t="str">
-        <v>온디바이스 AI 반도체 IP 및 NPU 솔루션 개발</v>
+        <v>타임폴리오, '공간정보 AI 기업' 메이사에 신규 투자 [fn마켓워치]</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>신규 투자 라운드</v>
       </c>
       <c r="J12" t="str">
-        <v>추가 투자 (유상증자)</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>미공개</v>
+        <v/>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>미공개</v>
+        <v/>
       </c>
       <c r="N12" t="str">
         <v/>
       </c>
       <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>0</v>
       </c>
-      <c r="R12" t="str">
-        <v>에이티넘인베스트먼트의 추가 투자 유치로 기존 투자자의 신뢰 및 후속 지원 확인</v>
-      </c>
       <c r="S12" t="str">
-        <v>온디바이스 AI 반도체 IP 분야로 글로벌 AI 엣지 컴퓨팅 시장 성장 수혜 가능</v>
+        <v>공간정보 AI 분야 특화 기업으로 틈새 시장 선점 가능성</v>
       </c>
       <c r="T12" t="str">
-        <v>서울창업허브 SBA 지원 우수기업 선정으로 성장성 및 기술력 외부 인정</v>
+        <v>타임폴리오 등 전문 기관투자자로부터 신규 투자 유치로 성장성 인정</v>
       </c>
       <c r="U12" t="str">
-        <v>공개된 재무정보 및 특허 데이터 부재로 실적·기술력 검증 어려움</v>
+        <v>스마트시티·자율주행·디지털트윈 등 성장 산업과 연계된 수요 확대 기대</v>
       </c>
       <c r="V12" t="str">
-        <v>비상장 가격 데이터 미형성으로 시장 내 유동성 및 밸류에이션 불투명</v>
+        <v>재무정보 미공개로 수익성 및 매출 규모 파악 불가</v>
       </c>
       <c r="W12" t="str">
-        <v>AI 반도체 IP 시장 내 ARM, Cadence 등 글로벌 대형 플레이어와의 경쟁 심화</v>
+        <v>특허 건수 0건으로 핵심 기술 보호 역량 및 기술 독자성 불확실</v>
       </c>
       <c r="X12" t="str">
-        <v>기술 성숙도 및 추가 투자 유치 진행 중으로 이르면 2026~2027년 IPO 가능성이 있으나 재무 공개 수준에 따라 시점 불확실</v>
+        <v>비상장 거래 데이터 부재로 시장에서의 유동성 및 밸류에이션 근거 희박</v>
       </c>
       <c r="Y12" t="str">
-        <v>[더벨][유증 디테일] 오픈엣지, 에이티넘인베로부터 추가 투자 유치</v>
+        <v>공간정보 AI 산업 성장성은 긍정적이나 재무 정보 및 기술 보호 현황 부족으로 IPO 시점 예측 어려움</v>
       </c>
       <c r="Z12" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604031441473560106026</v>
+        <v>http://www.fnnews.com/news/202604021510288489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B13" t="str">
-        <v>넥서스비</v>
+        <v>블룸에이아이</v>
       </c>
       <c r="C13" t="str">
-        <v>기타</v>
+        <v>IT</v>
       </c>
       <c r="D13" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H13" t="str">
-        <v>비상장 기업으로 구체적 제품·서비스 정보 미확인</v>
+        <v>[더벨][thebell interview | 블룸에이아이 밸류업] 김범수·박진영 대표 ...</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>시리즈C</v>
+        <v/>
       </c>
       <c r="K13" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="L13" t="str">
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>100+</v>
+        <v/>
       </c>
       <c r="N13" t="str">
         <v/>
       </c>
       <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>0</v>
       </c>
-      <c r="R13" t="str">
-        <v>국책금융기관인 산업은행이 시리즈C에 참여하여 신뢰도 및 안정성 확보</v>
-      </c>
       <c r="S13" t="str">
-        <v>시리즈C 단계 진입으로 일정 수준 이상의 사업 성숙도 및 트랙레코드 보유 추정</v>
+        <v>공동대표 체제로 더벨 인터뷰 노출 — 기관 투자자 대상 밸류업 활동 진행 중</v>
       </c>
       <c r="T13" t="str">
-        <v>100억 규모의 추가 자금 조달로 사업 확장 여력 확보</v>
+        <v>AI 분야 포지셔닝으로 현재 시장 트렌드에 부합하는 업종</v>
       </c>
       <c r="U13" t="str">
-        <v>재무정보 미공개로 매출·손익 등 핵심 펀더멘털 검증 불가</v>
+        <v>비상장주식 플랫폼(38커뮤니케이션 등)에 등록되어 유동성 확보 시도 중</v>
       </c>
       <c r="V13" t="str">
-        <v>특허 0건으로 기술적 해자 및 지식재산권 경쟁력 불명확</v>
+        <v>재무정보 전무 — 매출, 영업이익 등 핵심 지표 확인 불가</v>
       </c>
       <c r="W13" t="str">
-        <v>주요 사업 내용, 대표자, 설립연도 등 기본 정보 부재로 투자 판단 근거 부족</v>
+        <v>특허 0건 — 기술 독자성 및 IP 경쟁력 검증 어려움</v>
       </c>
       <c r="X13" t="str">
-        <v>산업은행 투자 유치로 IPO 가능성은 존재하나 공개 정보 부족으로 구체적 시점 예측 어려움</v>
+        <v>비상장 거래 데이터 부족(거래량·가격 미형성) — 시장 내 인지도 및 유동성 극히 낮음</v>
       </c>
       <c r="Y13" t="str">
-        <v>[더벨]넥서스비, 100억 시리즈C 돌입…산업은행 베팅</v>
+        <v>공개된 투자 이력·재무 데이터가 없어 IPO 시점 예측 불가, 밸류업 인터뷰 활동을 감안하면 중장기(3년 이상) 준비 단계로 추정</v>
       </c>
       <c r="Z13" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021151163520108335</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202603311441089560102228</v>
       </c>
     </row>
     <row r="14">
@@ -1445,79 +1474,79 @@
         <v>2026-04-07</v>
       </c>
       <c r="B14" t="str">
-        <v>닷</v>
+        <v>블룸에이아이</v>
       </c>
       <c r="C14" t="str">
         <v>IT</v>
       </c>
       <c r="D14" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H14" t="str">
-        <v>시각장애인용 점자 스마트 기기 및 접근성 기술 솔루션 개발 소셜벤처</v>
+        <v>[더벨][thebell interview | 블룸에이아이 밸류업] 김범수·박진영 대표 ...</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>최근 투자 라운드</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>43</v>
+        <v/>
       </c>
       <c r="L14" t="str">
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>43</v>
+        <v/>
       </c>
       <c r="N14" t="str">
         <v/>
       </c>
       <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>0</v>
       </c>
-      <c r="R14" t="str">
-        <v>소셜벤처로서 사회적 가치와 비즈니스 가치를 동시에 추구하는 차별화된 포지셔닝</v>
-      </c>
       <c r="S14" t="str">
-        <v>43억 신규 투자유치 성공으로 IPO 재도전을 위한 자금 확보</v>
+        <v>공동 대표 체제(김범수·박진영)로 더벨 인터뷰 노출 등 미디어 밸류업 활동 진행 중</v>
       </c>
       <c r="T14" t="str">
-        <v>접근성 기술 분야의 글로벌 시장 확장 가능성 및 ESG 트렌드 부합</v>
+        <v>AI 분야로 현재 시장 트렌드와 부합하는 업종</v>
       </c>
       <c r="U14" t="str">
-        <v>IPO '재도전' 표현에서 알 수 있듯 이전 상장 시도 실패 이력 존재</v>
+        <v>비상장 주식 시장에 등록되어 일정 수준의 시장 인지도 형성</v>
       </c>
       <c r="V14" t="str">
-        <v>재무정보 미공개로 수익성 및 매출 규모 검증 불가</v>
+        <v>재무정보 전혀 없어 실적·수익성 검증 불가</v>
       </c>
       <c r="W14" t="str">
-        <v>비상장 거래가 신한스팩18호와 연계된 스팩 합병 방식으로, 자체 상장 경쟁력 불확실</v>
+        <v>특허 0건으로 기술 독창성 및 지식재산권 보호 역량 매우 취약</v>
       </c>
       <c r="X14" t="str">
-        <v>신한스팩18호를 통한 스팩 합병 상장 방식으로 IPO 재도전 중이며, 2026년 내 상장 가시화 가능성 있으나 과거 실패 이력으로 불확실성 상존</v>
+        <v>투자 라운드 이력 미확인으로 VC 신뢰도 및 자금 조달 역량 파악 불가</v>
       </c>
       <c r="Y14" t="str">
-        <v>[더벨]'소셜벤처' 닷, 43억 투자유치…IPO 재도전 전망</v>
+        <v>현재 공개된 재무·투자 데이터가 전무하여 IPO 가능성 및 시점 판단 불가, 밸류업 활동 초기 단계로 추가 정보 확인 필요</v>
       </c>
       <c r="Z14" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021052204360105140</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202603311441089560102228</v>
       </c>
     </row>
     <row r="15">
@@ -1525,111 +1554,111 @@
         <v>2026-04-07</v>
       </c>
       <c r="B15" t="str">
-        <v>스탁키퍼</v>
+        <v>블룸에이아이</v>
       </c>
       <c r="C15" t="str">
-        <v>핀테크</v>
+        <v>IT</v>
       </c>
       <c r="D15" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>투자라운드:0/15 | 투자금액:0/15 | 밸류에이션:0/10 | 참여VC티어:0/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:4/5</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H15" t="str">
-        <v>한우 조각투자 플랫폼 '뱅카우' 운영 — 살아있는 한우에 소액 투자 가능한 애그테크·핀테크 서비스</v>
+        <v>[더벨][thebell interview | 블룸에이아이 밸류업] 김범수·박진영 대표 ...</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>시리즈B</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>70</v>
+        <v/>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>70+</v>
+        <v/>
       </c>
       <c r="N15" t="str">
         <v/>
       </c>
       <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>0</v>
       </c>
-      <c r="R15" t="str">
-        <v>한우 조각투자라는 독창적 애그테크·핀테크 니치 시장 선점</v>
-      </c>
       <c r="S15" t="str">
-        <v>시리즈B 클로징으로 기관 투자자 신뢰 확보 및 사업 지속 가능성 입증</v>
+        <v>공동대표 체제(김범수·박진영)로 경영 안정성 및 역할 분담 가능</v>
       </c>
       <c r="T15" t="str">
-        <v>실물 자산(한우) 기반 투자 구조로 가상자산 대비 규제 리스크 상대적으로 낮음</v>
+        <v>더벨 인터뷰 노출을 통한 투자자 대상 적극적 밸류업 행보</v>
       </c>
       <c r="U15" t="str">
-        <v>한우 가격 변동성 및 구제역 등 가축 질병 리스크가 투자 수익률에 직접 영향</v>
+        <v>비상장 주식 시장(38커뮤니케이션 등)에 등록되어 유동성 확보 시도 중</v>
       </c>
       <c r="V15" t="str">
-        <v>조각투자 관련 금융당국 규제 불확실성 — 증권성 판단 및 자본시장법 적용 가능성</v>
+        <v>재무정보 미공개로 수익성·매출 규모 파악 불가</v>
       </c>
       <c r="W15" t="str">
-        <v>공개된 재무정보·특허 미확인으로 수익성·기술 경쟁력 검증 어려움</v>
+        <v>특허 0건으로 기술 독창성 및 지식재산 보호 역량 불확실</v>
       </c>
       <c r="X15" t="str">
-        <v>시리즈B 단계로 IPO까지 상당한 성장 단계가 남아 있으며, 조각투자 규제 명확화 이후 빠르면 2027~2028년 코스닥 또는 스팩 합병 상장 가능성 검토 예상</v>
+        <v>규제 관련 데이터가 무관한 기사로 구성되어 있어 사업 리스크 파악 어려움</v>
       </c>
       <c r="Y15" t="str">
-        <v>[더벨]'뱅카우' 스탁키퍼, 70억 시리즈B 라운드 클로징</v>
+        <v>신한스팩18호와의 연계 가능성이 확인되며 스팩 합병 방식의 우회 상장 가능성 존재하나 구체적 시점은 미확인</v>
       </c>
       <c r="Z15" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011547179320109662</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202603311441089560102228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B16" t="str">
-        <v>블룸에이아이</v>
+        <v>스탁키퍼</v>
       </c>
       <c r="C16" t="str">
-        <v>IT</v>
+        <v>핀테크</v>
       </c>
       <c r="D16" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" t="str">
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>김범수, 박진영</v>
+        <v>-</v>
       </c>
       <c r="H16" t="str">
-        <v>AI 기반 서비스 제공 스타트업 (블룸에이아이)</v>
+        <v>[더벨]'뱅카우' 스탁키퍼, 70억 시리즈B 라운드 클로징</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>시리즈B</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>70</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1641,43 +1670,43 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>70</v>
       </c>
       <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>0</v>
       </c>
-      <c r="R16" t="str">
-        <v>공동 대표 체제(김범수·박진영)로 더벨 인터뷰 노출 등 미디어 밸류업 활동 진행 중</v>
-      </c>
       <c r="S16" t="str">
-        <v>AI 분야로 현재 시장 트렌드와 부합하는 업종</v>
+        <v>한우 조각투자라는 독특한 실물자산 기반 핀테크 니치 시장 선점</v>
       </c>
       <c r="T16" t="str">
-        <v>비상장 주식 시장에 등록되어 일정 수준의 시장 인지도 형성</v>
+        <v>시리즈B 클로징으로 성장 단계 진입 및 투자자 신뢰 확보</v>
       </c>
       <c r="U16" t="str">
-        <v>재무정보 전혀 없어 실적·수익성 검증 불가</v>
+        <v>농축산업과 금융기술의 결합으로 차별화된 비즈니스 모델 구축</v>
       </c>
       <c r="V16" t="str">
-        <v>특허 0건으로 기술 독창성 및 지식재산권 보호 역량 매우 취약</v>
+        <v>한우 가격 변동성 및 구제역 등 농축산 관련 외부 리스크에 직접 노출</v>
       </c>
       <c r="W16" t="str">
-        <v>투자 라운드 이력 미확인으로 VC 신뢰도 및 자금 조달 역량 파악 불가</v>
+        <v>조각투자 관련 금융규제 불확실성으로 사업 지속성 위협 가능</v>
       </c>
       <c r="X16" t="str">
-        <v>현재 공개된 재무·투자 데이터가 전무하여 IPO 가능성 및 시점 판단 불가, 밸류업 활동 초기 단계로 추가 정보 확인 필요</v>
+        <v>특허 0건으로 기술 경쟁력 및 진입장벽이 취약하고 모방 가능성 존재</v>
       </c>
       <c r="Y16" t="str">
-        <v>[더벨][thebell interview | 블룸에이아이 밸류업] 김범수·박진영 대표 ...</v>
+        <v>시리즈B 초기 단계로 IPO까지 상당한 시간이 필요하며, 규제 환경 안정화 및 수익성 확보 후 빠르면 2027~2028년경 가능성 검토 예상</v>
       </c>
       <c r="Z16" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202603311441089560102228</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011547179320109662</v>
       </c>
     </row>
     <row r="17">
@@ -1685,79 +1714,79 @@
         <v>2026-04-07</v>
       </c>
       <c r="B17" t="str">
-        <v>메이사</v>
+        <v>스탁키퍼</v>
       </c>
       <c r="C17" t="str">
-        <v>IT</v>
+        <v>핀테크</v>
       </c>
       <c r="D17" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H17" t="str">
-        <v>공간정보 AI 기술 기반 서비스 (3D 공간 데이터 분석 및 처리 솔루션)</v>
+        <v>[더벨]'뱅카우' 스탁키퍼, 70억 시리즈B 라운드 클로징</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>시리즈B</v>
       </c>
       <c r="J17" t="str">
-        <v>신규 투자 (라운드 미상)</v>
+        <v>70</v>
       </c>
       <c r="K17" t="str">
-        <v>미공개</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>미공개</v>
+        <v/>
       </c>
       <c r="M17" t="str">
-        <v>미공개</v>
+        <v/>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>70+</v>
       </c>
       <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>0</v>
       </c>
-      <c r="R17" t="str">
-        <v>공간정보 AI라는 틈새 기술 특화 분야로 차별화된 포지셔닝 가능</v>
-      </c>
       <c r="S17" t="str">
-        <v>타임폴리오 등 투자 전문기관의 신규 투자 유치로 외부 검증 확인</v>
+        <v>한우 조각투자라는 독창적 애그테크·핀테크 니치 시장 선점</v>
       </c>
       <c r="T17" t="str">
-        <v>스마트시티·자율주행·디지털트윈 등 공간정보 수요 급성장 시장과 연계 가능성</v>
+        <v>시리즈B 클로징으로 기관 투자자 신뢰 확보 및 사업 지속 가능성 입증</v>
       </c>
       <c r="U17" t="str">
-        <v>재무정보 미공개로 매출·수익성 등 핵심 펀더멘털 파악 불가</v>
+        <v>실물 자산(한우) 기반 투자 구조로 가상자산 대비 규제 리스크 상대적으로 낮음</v>
       </c>
       <c r="V17" t="str">
-        <v>특허 0건으로 기술 독점성 및 지식재산권 방어력이 취약</v>
+        <v>한우 가격 변동성 및 구제역 등 가축 질병 리스크가 투자 수익률에 직접 영향</v>
       </c>
       <c r="W17" t="str">
-        <v>비상장 거래 데이터 부재(신한스팩18호 연계 가능성 언급만 있어 유동성 불투명)</v>
+        <v>조각투자 관련 금융당국 규제 불확실성 — 증권성 판단 및 자본시장법 적용 가능성</v>
       </c>
       <c r="X17" t="str">
-        <v>공간정보 AI 성장성은 긍정적이나 재무·특허 정보 부족으로 단기 IPO 가능성 판단 어려우며, 스팩 합병 경로 검토 중인 것으로 추정됨</v>
+        <v>공개된 재무정보·특허 미확인으로 수익성·기술 경쟁력 검증 어려움</v>
       </c>
       <c r="Y17" t="str">
-        <v>타임폴리오, '공간정보 AI 기업' 메이사에 신규 투자 [fn마켓워치]</v>
+        <v>시리즈B 단계로 IPO까지 상당한 성장 단계가 남아 있으며, 조각투자 규제 명확화 이후 빠르면 2027~2028년 코스닥 또는 스팩 합병 상장 가능성 검토 예상</v>
       </c>
       <c r="Z17" t="str">
-        <v>http://www.fnnews.com/news/202604021510288489</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011547179320109662</v>
       </c>
     </row>
     <row r="18">
@@ -1765,114 +1794,114 @@
         <v>2026-04-07</v>
       </c>
       <c r="B18" t="str">
-        <v>위플로</v>
+        <v>스탁키퍼</v>
       </c>
       <c r="C18" t="str">
-        <v>IT</v>
+        <v>핀테크</v>
       </c>
       <c r="D18" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>투자라운드:10/15 | 투자금액:9/15 | 밸류에이션:0/10 | 참여VC티어:0/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:5/5</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="H18" t="str">
-        <v>AI 기반 진단 솔루션 개발 및 제공</v>
+        <v>[더벨]'뱅카우' 스탁키퍼, 70억 시리즈B 라운드 클로징</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>시리즈B</v>
       </c>
       <c r="J18" t="str">
-        <v>Pre-시리즈 A 이전 누적</v>
+        <v>70</v>
       </c>
       <c r="K18" t="str">
-        <v>63</v>
+        <v/>
       </c>
       <c r="L18" t="str">
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>118</v>
+        <v/>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>70</v>
       </c>
       <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>0</v>
       </c>
-      <c r="R18" t="str">
-        <v>AI 진단 솔루션이라는 고성장 분야에서 시리즈 A 단계까지 누적 118억원 투자 유치에 성공하며 투자자 신뢰 확보</v>
-      </c>
       <c r="S18" t="str">
-        <v>AI 기반 진단이라는 B2B 특화 기술 영역으로 높은 진입장벽 보유 가능성</v>
+        <v>한우 조각투자라는 독창적 대체투자 플랫폼으로 시장 내 차별화된 포지셔닝</v>
       </c>
       <c r="T18" t="str">
-        <v>시리즈 A 단계에서 55억원 규모의 단일 라운드 유치로 성장 모멘텀 확인</v>
+        <v>시리즈B 라운드 클로징으로 투자자 신뢰 및 사업 지속성 확보</v>
       </c>
       <c r="U18" t="str">
-        <v>공개된 재무정보 및 매출 데이터가 전무하여 실질적인 사업 성과 검증 불가</v>
+        <v>실물자산 기반 투자 플랫폼으로 인플레이션 헤지 수요 흡수 가능</v>
       </c>
       <c r="V18" t="str">
-        <v>특허 건수 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡할 수 있음</v>
+        <v>한우 가격 변동성 및 축산업 경기에 직접적으로 노출된 사업 구조</v>
       </c>
       <c r="W18" t="str">
-        <v>AI 진단 솔루션 시장 내 대기업 및 글로벌 경쟁사와의 경쟁 심화 리스크</v>
+        <v>조각투자 관련 금융당국 규제 불확실성 상존</v>
       </c>
       <c r="X18" t="str">
-        <v>누적 투자 118억원으로 초기 단계이며, 재무 정보 부재와 특허 미확보 등을 감안할 때 IPO까지는 최소 3~5년 이상 소요될 것으로 예상</v>
+        <v>재무정보 미공개로 수익성 및 성장성 검증 어려움</v>
       </c>
       <c r="Y18" t="str">
-        <v>AI 진단 솔루션 기업 위플로, 55억원 시리즈 A 유치…누적 118억원</v>
+        <v>시리즈B 단계로 IPO까지 추가 성장이 필요하며, 규제 환경 및 플랫폼 확장 속도에 따라 2027년 이후 가능성 검토 예상</v>
       </c>
       <c r="Z18" t="str">
-        <v>https://platum.kr/archives/284860</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011547179320109662</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B19" t="str">
-        <v>리벨리온</v>
+        <v>오픈엣지</v>
       </c>
       <c r="C19" t="str">
         <v>IT</v>
       </c>
       <c r="D19" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" t="str">
-        <v>2020</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>박성현</v>
+        <v>-</v>
       </c>
       <c r="H19" t="str">
-        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
+        <v>[더벨][유증 디테일] 오픈엣지, 에이티넘인베로부터 추가 투자 유치</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>추가 투자 (유상증자)</v>
       </c>
       <c r="J19" t="str">
-        <v>시리즈C</v>
+        <v>비공개</v>
       </c>
       <c r="K19" t="str">
-        <v>1000</v>
+        <v/>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1881,43 +1910,43 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>비공개</v>
       </c>
       <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>0</v>
       </c>
-      <c r="R19" t="str">
-        <v>AI 반도체(NPU) 분야 국내 선도 팹리스 기업으로 기술 경쟁력 보유</v>
-      </c>
       <c r="S19" t="str">
-        <v>SV인베스트먼트 등 주요 VC로부터 지속적인 투자 유치 이력</v>
+        <v>온디바이스 AI 및 엣지 AI 반도체 IP 분야 기술 전문성 보유로 AI 산업 성장 수혜 기대</v>
       </c>
       <c r="T19" t="str">
-        <v>AI 인프라 수요 급증으로 NPU 시장 성장 수혜 가능성</v>
+        <v>에이티넘인베스트먼트 등 국내 주요 VC로부터 지속적인 추가 투자 유치로 투자자 신뢰 확인</v>
       </c>
       <c r="U19" t="str">
-        <v>수집 데이터 부족으로 재무정보·특허·밸류에이션 등 핵심 정보 확인 불가</v>
+        <v>글로벌 NPU IP 시장 성장과 함께 팹리스·AI 반도체 수요 증가로 시장 성장성 높음</v>
       </c>
       <c r="V19" t="str">
-        <v>엔비디아·퀄컴 등 글로벌 AI 반도체 기업과의 극심한 경쟁</v>
+        <v>재무정보 미공개로 매출·수익성 등 기초 펀더멘털 검증 불가</v>
       </c>
       <c r="W19" t="str">
-        <v>비상장 가격 데이터가 신한스팩18호 관련 정보와 혼재되어 기업 특정 신뢰도 낮음</v>
+        <v>ARM, Cadence 등 글로벌 대형 반도체 IP 기업과의 경쟁 심화로 시장 확대 난항 가능성</v>
       </c>
       <c r="X19" t="str">
-        <v>수집 데이터 불충분으로 IPO 시점 특정 어려우나, AI 반도체 섹터 관심도 고려 시 2025~2026년 내 추진 가능성 존재</v>
+        <v>특허 건수 0건으로 기록되어 핵심 기술 보호 체계 및 지식재산 경쟁력 불확실</v>
       </c>
       <c r="Y19" t="str">
-        <v>[더벨][VC 인사 풍향계] SV인베, VC조직 통합…오탁근·강민구·이효상 ...</v>
+        <v>AI 반도체 IP 섹터 관심 지속 및 VC 후속 투자 유치 흐름 감안 시 2026~2027년 코스닥 IPO 추진 가능성 있으나, 재무 공개 및 고객사 확보 성과가 관건</v>
       </c>
       <c r="Z19" t="str">
-        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021525063440101161</v>
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604031441473560106026</v>
       </c>
     </row>
     <row r="20">
@@ -1925,213 +1954,1829 @@
         <v>2026-04-07</v>
       </c>
       <c r="B20" t="str">
-        <v>퓨리오사AI</v>
+        <v>오픈엣지</v>
       </c>
       <c r="C20" t="str">
         <v>IT</v>
       </c>
       <c r="D20" t="str">
-        <v>미등록(비상장추정)</v>
+        <v/>
       </c>
       <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>-</v>
+      </c>
+      <c r="H20" t="str">
+        <v>[더벨][유증 디테일] 오픈엣지, 에이티넘인베로부터 추가 투자 유치</v>
+      </c>
+      <c r="I20" t="str">
+        <v>추가 투자 (유상증자)</v>
+      </c>
+      <c r="J20" t="str">
+        <v>미공개</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>미공개</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20" t="str">
+        <v>에이티넘인베스트먼트의 추가 투자 유치로 기존 투자자의 신뢰 및 후속 지원 확인</v>
+      </c>
+      <c r="T20" t="str">
+        <v>온디바이스 AI 반도체 IP 분야로 글로벌 AI 엣지 컴퓨팅 시장 성장 수혜 가능</v>
+      </c>
+      <c r="U20" t="str">
+        <v>서울창업허브 SBA 지원 우수기업 선정으로 성장성 및 기술력 외부 인정</v>
+      </c>
+      <c r="V20" t="str">
+        <v>공개된 재무정보 및 특허 데이터 부재로 실적·기술력 검증 어려움</v>
+      </c>
+      <c r="W20" t="str">
+        <v>비상장 가격 데이터 미형성으로 시장 내 유동성 및 밸류에이션 불투명</v>
+      </c>
+      <c r="X20" t="str">
+        <v>AI 반도체 IP 시장 내 ARM, Cadence 등 글로벌 대형 플레이어와의 경쟁 심화</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>기술 성숙도 및 추가 투자 유치 진행 중으로 이르면 2026~2027년 IPO 가능성이 있으나 재무 공개 수준에 따라 시점 불확실</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604031441473560106026</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B21" t="str">
+        <v>오픈엣지</v>
+      </c>
+      <c r="C21" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21">
+        <v>1.3</v>
+      </c>
+      <c r="F21" t="str">
+        <v>투자라운드:0/15 | 투자금액:0/15 | 밸류에이션:0/10 | 참여VC티어:3/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:5/5</v>
+      </c>
+      <c r="G21" t="str">
+        <v>-</v>
+      </c>
+      <c r="H21" t="str">
+        <v>[더벨][유증 디테일] 오픈엣지, 에이티넘인베로부터 추가 투자 유치</v>
+      </c>
+      <c r="I21" t="str">
+        <v>추가 투자 (유상증자)</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21" t="str">
+        <v>엣지 AI 반도체 NPU IP 분야 국내 선도 기업으로 기술 경쟁력 보유</v>
+      </c>
+      <c r="T21" t="str">
+        <v>에이티넘인베스트먼트 등 기관 투자자로부터 지속적인 추가 투자 유치로 신뢰도 확보</v>
+      </c>
+      <c r="U21" t="str">
+        <v>AI 온디바이스 수요 급증에 따른 엣지 AI 칩 시장 성장 수혜 가능성 높음</v>
+      </c>
+      <c r="V21" t="str">
+        <v>수집 재무정보 부재로 매출·수익성 확인 불가, 적자 지속 가능성 존재</v>
+      </c>
+      <c r="W21" t="str">
+        <v>ARM, 퀄컴 등 글로벌 대형 반도체 기업과의 NPU IP 시장 경쟁 심화</v>
+      </c>
+      <c r="X21" t="str">
+        <v>비상장 유통 데이터 미비(프리스타 가격 없음)로 시장 내 유동성 및 밸류에이션 불투명</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>신한스팩18호 관련 정보가 비상장 데이터에 등록되어 있어 스팩 합병 상장 추진 가능성이 있으며, 2026년 내 상장 시도 가능성 주목</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604031441473560106026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B22" t="str">
+        <v>위플로</v>
+      </c>
+      <c r="C22" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>-</v>
+      </c>
+      <c r="H22" t="str">
+        <v>AI 진단 솔루션 기업 위플로, 55억원 시리즈 A 유치…누적 118억원</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Pre-시리즈 A 이전 누적</v>
+      </c>
+      <c r="J22" t="str">
+        <v>63</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v>118</v>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22" t="str">
+        <v>AI 진단 솔루션이라는 고성장 분야에서 시리즈 A 단계까지 누적 118억원 투자 유치에 성공하며 투자자 신뢰 확보</v>
+      </c>
+      <c r="T22" t="str">
+        <v>AI 기반 진단이라는 B2B 특화 기술 영역으로 높은 진입장벽 보유 가능성</v>
+      </c>
+      <c r="U22" t="str">
+        <v>시리즈 A 단계에서 55억원 규모의 단일 라운드 유치로 성장 모멘텀 확인</v>
+      </c>
+      <c r="V22" t="str">
+        <v>공개된 재무정보 및 매출 데이터가 전무하여 실질적인 사업 성과 검증 불가</v>
+      </c>
+      <c r="W22" t="str">
+        <v>특허 건수 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡할 수 있음</v>
+      </c>
+      <c r="X22" t="str">
+        <v>AI 진단 솔루션 시장 내 대기업 및 글로벌 경쟁사와의 경쟁 심화 리스크</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>누적 투자 118억원으로 초기 단계이며, 재무 정보 부재와 특허 미확보 등을 감안할 때 IPO까지는 최소 3~5년 이상 소요될 것으로 예상</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>https://platum.kr/archives/284860</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B23" t="str">
+        <v>위플로</v>
+      </c>
+      <c r="C23" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>1.8</v>
+      </c>
+      <c r="F23" t="str">
+        <v>투자라운드:0/15 | 투자금액:9/15 | 밸류에이션:0/10 | 참여VC티어:0/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:4/5</v>
+      </c>
+      <c r="G23" t="str">
+        <v>-</v>
+      </c>
+      <c r="H23" t="str">
+        <v>AI 예지정비 전문 위플로, 55억 시리즈 A 투자 유치</v>
+      </c>
+      <c r="I23" t="str">
+        <v>시리즈 A</v>
+      </c>
+      <c r="J23" t="str">
+        <v>55</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v>55</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23" t="str">
+        <v>AI 예지정비라는 산업용 AI 틈새시장 선점으로 차별화된 포지셔닝 확보</v>
+      </c>
+      <c r="T23" t="str">
+        <v>시리즈 A 투자 유치 성공으로 사업 확장을 위한 초기 자금 확보</v>
+      </c>
+      <c r="U23" t="str">
+        <v>제조·설비 분야의 예지정비 수요 증가 트렌드와 맞닿은 성장 가능성</v>
+      </c>
+      <c r="V23" t="str">
+        <v>특허 0건으로 핵심 기술 보호 수단 부재 및 경쟁사 모방 위험</v>
+      </c>
+      <c r="W23" t="str">
+        <v>재무정보 미공개로 수익성·매출 규모 등 기본 재무 검증 불가</v>
+      </c>
+      <c r="X23" t="str">
+        <v>시장 내 대형 IT·AI 기업들과의 경쟁 심화 가능성</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>시리즈 A 초기 단계로 IPO까지 상당한 시간이 필요하며, 기술 고도화 및 매출 트랙레코드 확보 후 이르면 2027~2028년 이후 가능성 검토 예상</v>
+      </c>
+      <c r="Z23" t="str">
+        <v>https://www.aitimes.com/news/articleView.html?idxno=208866</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B24" t="str">
+        <v>텔레픽스</v>
+      </c>
+      <c r="C24" t="str">
+        <v>기타</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>-</v>
+      </c>
+      <c r="H24" t="str">
+        <v>[더벨][VC x 스타트업 동행] '매출 0'에서 유럽 수출까지…SBVA·텔레픽스...</v>
+      </c>
+      <c r="I24" t="str">
+        <v>SBVA 투자 라운드</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24" t="str">
+        <v>매출 0에서 유럽 수출까지 성장한 실적, 글로벌 시장 개척 능력 입증</v>
+      </c>
+      <c r="T24" t="str">
+        <v>SBVA 등 주요 VC의 투자 유치로 사업성과 기술력 검증</v>
+      </c>
+      <c r="U24" t="str">
+        <v>우주·위성 분야 성장 섹터 내 선도적 포지셔닝 가능성</v>
+      </c>
+      <c r="V24" t="str">
+        <v>재무정보 미공개로 수익성 및 현금흐름 파악 불가</v>
+      </c>
+      <c r="W24" t="str">
+        <v>특허 0건으로 핵심 기술 보호 체계 미흡, 경쟁사 모방 리스크 존재</v>
+      </c>
+      <c r="X24" t="str">
+        <v>우주항공 규제 환경 불확실성 및 정부 수요 의존도 리스크</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>신한스팩18호와의 연관 정황이 있어 스팩 합병 상장 가능성이 있으나, 재무 정보 부재로 구체적 시점 예측 어려움</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604011519406360102666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B25" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C25" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>-</v>
+      </c>
+      <c r="H25" t="str">
+        <v>[더벨]교보증권, 퓨리오사AI 투자 검토…1000억 이하 가닥</v>
+      </c>
+      <c r="I25" t="str">
+        <v>시리즈 D (교보증권 검토)</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1000억 이하</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v>미상</v>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25" t="str">
+        <v>국내 독자 AI 반도체(NPU) 기술력 보유로 차별화된 팹리스 포지셔닝</v>
+      </c>
+      <c r="T25" t="str">
+        <v>교보증권 등 기관 투자자의 지속적 투자 검토로 시장 신뢰도 확인</v>
+      </c>
+      <c r="U25" t="str">
+        <v>글로벌 AI 인프라 수요 급증에 따른 국산 AI 반도체 수요 증가 수혜 기대</v>
+      </c>
+      <c r="V25" t="str">
+        <v>엔비디아 등 글로벌 빅테크와의 기술·자본력 격차로 시장 침투 어려움</v>
+      </c>
+      <c r="W25" t="str">
+        <v>재무정보 미공개로 수익성 및 현금흐름 검증 불가</v>
+      </c>
+      <c r="X25" t="str">
+        <v>AI 반도체 시장의 빠른 기술 변화로 제품 경쟁력 유지 불확실성 존재</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>국내 AI 반도체 대표 기업으로 관심은 높으나, 글로벌 경쟁 심화 및 수익화 검증 필요로 IPO는 2027~2028년 이후 가능성으로 전망</v>
+      </c>
+      <c r="Z25" t="str">
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021616402280106871</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B26" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C26" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
         <v>8</v>
       </c>
-      <c r="F20" t="str">
-        <v>2017</v>
-      </c>
-      <c r="G20" t="str">
-        <v>백준호</v>
-      </c>
-      <c r="H20" t="str">
-        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
-      </c>
-      <c r="I20" t="str">
-        <v>10000</v>
-      </c>
-      <c r="J20" t="str">
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>-</v>
+      </c>
+      <c r="H26" t="str">
+        <v>[더벨]교보증권, 퓨리오사AI 투자 검토…1000억 이하 가닥</v>
+      </c>
+      <c r="I26" t="str">
         <v>교보증권 투자 검토</v>
       </c>
-      <c r="K20" t="str">
+      <c r="J26" t="str">
         <v>1000이하</v>
       </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v>3600</v>
       </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
         <v>2026.04.20~04.21</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q26" t="str">
         <v>미등록</v>
       </c>
-      <c r="Q20">
+      <c r="R26">
         <v>0</v>
       </c>
-      <c r="R20" t="str">
+      <c r="S26" t="str">
         <v>국내 유일 독자 AI 반도체(NPU) 풀스택 설계 역량 보유로 기술 희소성 높음</v>
       </c>
-      <c r="S20" t="str">
+      <c r="T26" t="str">
         <v>현대차·LG전자·KT 등 대기업 전략적 투자자 확보로 고객 파이프라인 및 신뢰도 우수</v>
       </c>
-      <c r="T20" t="str">
+      <c r="U26" t="str">
         <v>AI 인프라 수요 급증에 따른 엣지·데이터센터 NPU 시장 고성장 수혜 직접적</v>
       </c>
-      <c r="U20" t="str">
+      <c r="V26" t="str">
         <v>엔비디아·AMD 등 글로벌 빅테크와의 기술력·자본력 격차로 시장 침투 난이도 높음</v>
       </c>
-      <c r="V20" t="str">
+      <c r="W26" t="str">
         <v>매출 본격화 전 지속적 R&amp;D 비용 소요로 수익성 확보 시점 불확실</v>
       </c>
-      <c r="W20" t="str">
+      <c r="X26" t="str">
         <v>교보증권 투자 검토가 1000억 이하로 가닥 잡히며 밸류에이션 협의 난항 가능성</v>
       </c>
-      <c r="X20" t="str">
+      <c r="Y26" t="str">
         <v>AI 반도체 업종 프리미엄과 대형 VC·전략적 투자자 라인업을 감안하면 2026~2027년 코스닥 또는 코스피 상장 추진 가능성 높음</v>
       </c>
-      <c r="Y20" t="str">
+      <c r="Z26" t="str">
+        <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021616402280106871</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B27" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C27" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>2.8</v>
+      </c>
+      <c r="F27" t="str">
+        <v>투자라운드:0/15 | 투자금액:15/15 | 밸류에이션:0/10 | 참여VC티어:3/10 | 밸류상승률:5/20 | 매출성장률:0/20 | 특허수:0/5 | 인증허가:5/5</v>
+      </c>
+      <c r="G27" t="str">
+        <v>-</v>
+      </c>
+      <c r="H27" t="str">
         <v>[더벨]교보증권, 퓨리오사AI 투자 검토…1000억 이하 가닥</v>
       </c>
-      <c r="Z20" t="str">
+      <c r="I27" t="str">
+        <v>Series D (예정/검토)</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1000억 이하</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v>확인 불가</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27" t="str">
+        <v>국내 독자 NPU(신경망처리장치) 설계 역량 보유로 AI 반도체 국산화 선도</v>
+      </c>
+      <c r="T27" t="str">
+        <v>대형 증권사(교보증권) 등 기관투자자의 투자 검토가 이어질 만큼 시장 신뢰도 확보</v>
+      </c>
+      <c r="U27" t="str">
+        <v>글로벌 AI 인프라 수요 급증에 따른 AI 가속기 시장 성장 수혜 가능성</v>
+      </c>
+      <c r="V27" t="str">
+        <v>엔비디아, AMD 등 글로벌 빅테크와의 기술 및 점유율 격차 극복 과제</v>
+      </c>
+      <c r="W27" t="str">
+        <v>재무정보 미공개로 수익성·현금흐름 검증 불가, 투자자 정보 비대칭 위험</v>
+      </c>
+      <c r="X27" t="str">
+        <v>비상장 거래 데이터 부재(가격 정보 미형성)로 유동성 및 시장가치 산정 어려움</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>교보증권 등 기관 투자 검토가 진행 중인 단계로 IPO는 이르면 2026~2027년 가능성이 있으나, 재무 공개 및 수익화 가시성 확보가 선행 조건</v>
+      </c>
+      <c r="Z27" t="str">
         <v>https://www.thebell.co.kr/free/content/ArticleView.asp?key=202604021616402280106871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B28" t="str">
+        <v>프로티어바이오텍</v>
+      </c>
+      <c r="C28" t="str">
+        <v>바이오</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>-</v>
+      </c>
+      <c r="H28" t="str">
+        <v>프로티어바이오텍, pre-A 35억..'분자접착제·DAC' 개발</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Pre-A</v>
+      </c>
+      <c r="J28" t="str">
+        <v>35</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>35</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v>2026.04.20~04.21</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>미등록</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28" t="str">
+        <v>분자접착제 및 DAC 등 글로벌 신약 트렌드에 부합하는 혁신 플랫폼 기술 보유</v>
+      </c>
+      <c r="T28" t="str">
+        <v>표적단백질분해(TPD) 분야는 글로벌 빅파마의 높은 관심과 대형 기술이전 사례가 다수 존재하는 고성장 시장</v>
+      </c>
+      <c r="U28" t="str">
+        <v>Pre-A 단계에서 35억 유치로 초기 사업화 자금 확보, 향후 추가 라운드 가능성 존재</v>
+      </c>
+      <c r="V28" t="str">
+        <v>특허 등록 건수 0건으로 핵심 기술의 지식재산권 보호 체계가 미흡하여 기술 방어력 취약</v>
+      </c>
+      <c r="W28" t="str">
+        <v>재무정보 미공개로 매출·손익 현황 파악 불가, 투자 판단 근거 부족</v>
+      </c>
+      <c r="X28" t="str">
+        <v>Pre-A 초기 단계로 임상 진입까지 장기간 및 대규모 추가 자금 소요 예상, 밸류에이션 불확실성 높음</v>
+      </c>
+      <c r="Y28" t="str">
+        <v>현재 Pre-A 초기 단계로 임상 데이터 축적 및 후속 투자 유치가 선행되어야 하며, IPO 가능성은 존재하나 최소 5년 이상 소요 예상</v>
+      </c>
+      <c r="Z28" t="str">
+        <v>https://www.biospectator.com/view/news_view.php?varAtcId=28333</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L28"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>기준일: 2026-04-07 | 전영업일: 2026-04-06</v>
+        <v>날짜</v>
+      </c>
+      <c r="B1" t="str">
+        <v>회사명</v>
+      </c>
+      <c r="C1" t="str">
+        <v>섹터</v>
+      </c>
+      <c r="D1" t="str">
+        <v>한줄소개</v>
+      </c>
+      <c r="E1" t="str">
+        <v>중점기술</v>
+      </c>
+      <c r="F1" t="str">
+        <v>핵심경쟁력</v>
+      </c>
+      <c r="G1" t="str">
+        <v>타겟시장</v>
+      </c>
+      <c r="H1" t="str">
+        <v>주요고객사</v>
+      </c>
+      <c r="I1" t="str">
+        <v>비즈니스모델</v>
+      </c>
+      <c r="J1" t="str">
+        <v>경쟁사</v>
+      </c>
+      <c r="K1" t="str">
+        <v>성장전략</v>
+      </c>
+      <c r="L1" t="str">
+        <v>주요제품서비스</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>급등 1개 | 급락 1개 | 총 2개 종목</v>
+        <v>2026-04-06</v>
+      </c>
+      <c r="B2" t="str">
+        <v>넥서스비</v>
+      </c>
+      <c r="C2" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>B2B 기술 기반 솔루션 제공 기업 (정확한 제품·서비스 정보 확인 불가)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B3" t="str">
+        <v>넥서스비</v>
+      </c>
+      <c r="C3" t="str">
+        <v>기타</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>비상장 기업으로 구체적 제품·서비스 정보 미확인</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>회사명</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B4" t="str">
-        <v>기준일</v>
+        <v>넥서스비</v>
       </c>
       <c r="C4" t="str">
-        <v>38_전일가</v>
+        <v>IT</v>
       </c>
       <c r="D4" t="str">
-        <v>38_현재가</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>38_변동폭</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>증권플러스_전일가</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>증권플러스_현재가</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>증권플러스_변동폭</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>최대변동폭</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>알림</v>
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>B2B 기반 IT 솔루션 및 플랫폼 서비스</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>버킷플레이스</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-07</v>
+        <v>닷</v>
       </c>
       <c r="C5" t="str">
-        <v>30,000</v>
+        <v>기타</v>
       </c>
       <c r="D5" t="str">
-        <v>25,500</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>-15.0%</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>-15.0%</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>🔵 급락</v>
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>시각장애인용 점자 스마트 기기 및 AI 기반 보조기술 솔루션 개발 소셜벤처</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>컬리</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B6" t="str">
+        <v>닷</v>
+      </c>
+      <c r="C6" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>시각장애인용 점자 스마트 기기 및 접근성 기술 솔루션 개발 소셜벤처</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>2026-04-07</v>
       </c>
-      <c r="C6" t="str">
-        <v>45,000</v>
-      </c>
-      <c r="D6" t="str">
-        <v>51,000</v>
-      </c>
-      <c r="E6" t="str">
-        <v>+13.3%</v>
-      </c>
-      <c r="F6" t="str">
-        <v>-</v>
-      </c>
-      <c r="G6" t="str">
-        <v>-</v>
-      </c>
-      <c r="H6" t="str">
-        <v>-</v>
-      </c>
-      <c r="I6" t="str">
-        <v>+13.3%</v>
-      </c>
-      <c r="J6" t="str">
-        <v>🔴 급등</v>
+      <c r="B7" t="str">
+        <v>닷</v>
+      </c>
+      <c r="C7" t="str">
+        <v>기타</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>시각장애인용 점자 스마트 기기 등 보조공학 기반 소셜벤처 제품·서비스</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B8" t="str">
+        <v>리벨리온</v>
+      </c>
+      <c r="C8" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 스타트업</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B9" t="str">
+        <v>리벨리온</v>
+      </c>
+      <c r="C9" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B10" t="str">
+        <v>메이사</v>
+      </c>
+      <c r="C10" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>공간정보 AI 기반 3D 지도·디지털 트윈 솔루션 제공</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B11" t="str">
+        <v>메이사</v>
+      </c>
+      <c r="C11" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>공간정보 AI 기술 기반 서비스 (3D 공간 데이터 분석 및 처리 솔루션)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>메이사</v>
+      </c>
+      <c r="C12" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>공간정보 AI 기술 기반 3D 공간 데이터 분석 및 솔루션 제공</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B13" t="str">
+        <v>블룸에이아이</v>
+      </c>
+      <c r="C13" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>AI 기반 서비스 개발 및 제공 (밸류업 인터뷰 기반 추정)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B14" t="str">
+        <v>블룸에이아이</v>
+      </c>
+      <c r="C14" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>AI 기반 서비스 제공 스타트업 (블룸에이아이)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B15" t="str">
+        <v>블룸에이아이</v>
+      </c>
+      <c r="C15" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>AI 기반 서비스 개발 및 제공 (밸류업 추진 중인 AI 스타트업)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B16" t="str">
+        <v>스탁키퍼</v>
+      </c>
+      <c r="C16" t="str">
+        <v>핀테크</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>한우 조각투자 플랫폼 '뱅카우' 운영</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B17" t="str">
+        <v>스탁키퍼</v>
+      </c>
+      <c r="C17" t="str">
+        <v>핀테크</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>한우 조각투자 플랫폼 '뱅카우' 운영 — 살아있는 한우에 소액 투자 가능한 애그테크·핀테크 서비스</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B18" t="str">
+        <v>스탁키퍼</v>
+      </c>
+      <c r="C18" t="str">
+        <v>핀테크</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>한우 조각투자 플랫폼 '뱅카우' 운영</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B19" t="str">
+        <v>오픈엣지</v>
+      </c>
+      <c r="C19" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>온디바이스 AI 반도체 NPU IP 설계 및 엣지 AI 솔루션 제공</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B20" t="str">
+        <v>오픈엣지</v>
+      </c>
+      <c r="C20" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>온디바이스 AI 반도체 IP 및 NPU 솔루션 개발</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B21" t="str">
+        <v>오픈엣지</v>
+      </c>
+      <c r="C21" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>엣지 AI 반도체 NPU IP 설계 및 솔루션 제공</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B22" t="str">
+        <v>위플로</v>
+      </c>
+      <c r="C22" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>AI 기반 진단 솔루션 개발 및 제공</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B23" t="str">
+        <v>위플로</v>
+      </c>
+      <c r="C23" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>AI 기반 예지정비(Predictive Maintenance) 솔루션 제공</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B24" t="str">
+        <v>텔레픽스</v>
+      </c>
+      <c r="C24" t="str">
+        <v>기타</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>우주·위성 통신 기술 기반 서비스 및 유럽 수출 사업</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B25" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C25" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B26" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C26" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>AI 반도체(NPU) 설계 및 개발 전문 팹리스 기업</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B27" t="str">
+        <v>퓨리오사AI</v>
+      </c>
+      <c r="C27" t="str">
+        <v>IT</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>AI 반도체(NPU) 설계 및 추론용 AI 가속기 개발</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B28" t="str">
+        <v>프로티어바이오텍</v>
+      </c>
+      <c r="C28" t="str">
+        <v>바이오</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>분자접착제(Molecular Glue) 및 DAC(분해유도 항체접합체) 기반 신약 개발</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>전영업일 가격 데이터 없음 (첫째 날 실행)</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>